--- a/Result/profitability/8097.xlsx
+++ b/Result/profitability/8097.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-1.18</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3375</v>
+        <v>-0.4087499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>14.47125</v>
+        <v>10.82875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.1</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.345</v>
+        <v>-0.4175</v>
       </c>
       <c r="N3" t="n">
-        <v>11.34875</v>
+        <v>9.576250000000002</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.48</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.30625</v>
+        <v>-0.365</v>
       </c>
       <c r="N4" t="n">
-        <v>10.78625</v>
+        <v>8.173750000000002</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.28</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.47375</v>
+        <v>-0.41</v>
       </c>
       <c r="N5" t="n">
-        <v>8.172500000000001</v>
+        <v>6.153750000000002</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>-0.31</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3975</v>
+        <v>-0.45</v>
       </c>
       <c r="N6" t="n">
-        <v>5.986250000000002</v>
+        <v>8.060000000000002</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-1.33</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.58125</v>
       </c>
       <c r="N7" t="n">
-        <v>7.410000000000002</v>
+        <v>8.007500000000002</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.79</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6287499999999999</v>
+        <v>-0.5900000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>7.267500000000002</v>
+        <v>7.912500000000001</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>-0.51375</v>
       </c>
       <c r="N11" t="n">
-        <v>9.008750000000001</v>
+        <v>9.008750000000003</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8097</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>86</v>
+      </c>
+      <c r="D75" t="n">
+        <v>79</v>
+      </c>
+      <c r="E75" t="n">
+        <v>7</v>
+      </c>
+      <c r="F75" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-18</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-21.31%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-25</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-25</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.24125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.4305555555555556</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>1.761092150170648</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.5543478260869565</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-16.15</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.6662541254125413</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
